--- a/processed-data/21_Xenium/01_xenium_panel/Xenium_hBrain_annotation.xlsx
+++ b/processed-data/21_Xenium/01_xenium_panel/Xenium_hBrain_annotation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/21_Xenium/01_xenium_panel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9556A66-DA9D-B446-9D58-368B25CFFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{F9556A66-DA9D-B446-9D58-368B25CFFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530FD05D-A41C-4349-B313-51DCCFADC697}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{C96CE3EF-4A07-9F41-9A2B-D338CB28F125}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
   <si>
     <t>Annotation</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>Glia</t>
-  </si>
-  <si>
-    <t>Neruon</t>
   </si>
   <si>
     <t>Excit</t>
@@ -1102,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
         <v>32</v>
@@ -1133,10 +1130,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>35</v>
@@ -1161,10 +1158,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
         <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>35</v>
@@ -1175,10 +1172,10 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>35</v>
@@ -1198,7 +1195,7 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1206,13 +1203,13 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1220,16 +1217,16 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1237,16 +1234,16 @@
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1254,16 +1251,16 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1271,13 +1268,13 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1285,16 +1282,16 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1302,13 +1299,13 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1316,16 +1313,16 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1333,13 +1330,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -1347,13 +1344,13 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1361,13 +1358,13 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1375,16 +1372,16 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1392,16 +1389,16 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -1409,16 +1406,16 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -1426,16 +1423,16 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1443,16 +1440,16 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1460,16 +1457,16 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1477,13 +1474,13 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1494,10 +1491,10 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -1505,13 +1502,13 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -1519,13 +1516,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
         <v>63</v>
       </c>
-      <c r="D28" t="s">
-        <v>64</v>
-      </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -1536,10 +1533,10 @@
         <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/processed-data/21_Xenium/01_xenium_panel/Xenium_hBrain_annotation.xlsx
+++ b/processed-data/21_Xenium/01_xenium_panel/Xenium_hBrain_annotation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lieberinstitute-my.sharepoint.com/personal/louise_huuki_libd_org/Documents/LIBD_code/LFF_spatial_ERC/processed-data/21_Xenium/01_xenium_panel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{F9556A66-DA9D-B446-9D58-368B25CFFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{530FD05D-A41C-4349-B313-51DCCFADC697}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{F9556A66-DA9D-B446-9D58-368B25CFFAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08BAE2B3-BED1-D148-A272-E95DCC9CF88F}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{C96CE3EF-4A07-9F41-9A2B-D338CB28F125}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="65">
   <si>
     <t>Annotation</t>
   </si>
@@ -1301,6 +1301,9 @@
       <c r="B14" t="s">
         <v>57</v>
       </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
       <c r="D14" t="s">
         <v>34</v>
       </c>
